--- a/stories/arbres/ATOM-EMO.LEX.004-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amandine arrose les pots avec papa. Un oiseau s'envole tout près. Voup. Amandine sent son cœur vite. Ses épaules sautent. Elle dit : je suis surprise. La cause, c'est l'oiseau. Papa dit : d'abord respirer. Ensuite comprendre. Amandine souffle une grande fois. Elle respire encore. Elle regarde. C'est un merle. Il picore. Rien n'est cassé. Amandine dit : je veux comprendre. Plus tard, à la cuisine, maman ouvre un placard. Une boîte glisse. Clac. Amandine sent encore son cœur. Elle dit : je suis surprise. Même leçon, autre lieu. Elle souffle. Elle respire. Elle regarde. C'est la boîte à farine. Elle veut comprendre. Maman sourit. Être surpris, on peut respirer. Puis on cherche à comprendre.</t>
+          <t>Amandine arrose les pots avec papa. Un oiseau s'envole tout près. Voup. Amandine sent son cœur vite. Ses épaules sautent. Je suis surprise. La cause, c'est l'oiseau. D'abord respirer. Ensuite comprendre. Amandine souffle une grande fois. Elle respire encore. Elle regarde. C'est un merle. Il picore. Rien n'est cassé. Je veux comprendre. Plus tard, à la cuisine, maman ouvre un placard. Une boîte glisse. Clac. Amandine sent encore son cœur. Je suis surprise. Même leçon, autre lieu. Elle souffle. Elle respire. Elle regarde. C'est la boîte à farine. Elle veut comprendre. Maman sourit. Être surpris, on peut respirer. Puis on cherche à comprendre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,19 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Amandine arrose les pots avec papa. Un oiseau s'envole tout près. Voup. Amandine sent son cœur vite. Ses épaules sautent.
+narrateur|Je suis surprise.
+narrateur|La cause, c'est l'oiseau.
+papa|D'abord respirer. Ensuite comprendre.
+narrateur|Amandine souffle une grande fois. Elle respire encore. Elle regarde. C'est un merle. Il picore. Rien n'est cassé.
+enfant-f|Je veux comprendre. Plus tard, à la cuisine, maman ouvre un placard.
+narrateur|Une boîte glisse. Clac. Amandine sent encore son cœur.
+narrateur|Je suis surprise. Même leçon, autre lieu. Elle souffle. Elle respire.
+narrateur|Elle regarde. C'est la boîte à farine. Elle veut comprendre. Maman sourit. Être surpris, on peut respirer. Puis on cherche à comprendre.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1498,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Amandine est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
     </row>
@@ -1637,6 +1671,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Amandine a nommé : surprise. Au jardin, puis à la cuisine. Elle a respiré. Elle a voulu comprendre.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1834,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Amandine range l'arrosoir. Papa referme le placard.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +2001,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2024,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2041,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-07.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1318,6 +1323,7 @@
 narrateur|Elle regarde. C'est la boîte à farine. Elle veut comprendre. Maman sourit. Être surpris, on peut respirer. Puis on cherche à comprendre.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1505,6 +1511,7 @@
           <t>narrateur|Amandine est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1676,6 +1683,7 @@
           <t>narrateur|Amandine a nommé : surprise. Au jardin, puis à la cuisine. Elle a respiré. Elle a voulu comprendre.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1839,6 +1847,7 @@
           <t>narrateur|Amandine range l'arrosoir. Papa referme le placard.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2006,6 +2015,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2024,7 +2034,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2048,6 +2058,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2062,7 +2086,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2249,6 +2273,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-EMO.LEX.004-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-07.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Amandine est surprise deux fois</t>
+          <t>Nina, le merle et la farine</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Nina est surprise par un merle, puis par une boîte à farine. Elle souffle. Elle comprend.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Amandine arrose les pots avec papa. Un oiseau s'envole tout près. Voup. Amandine sent son cœur vite. Ses épaules sautent. Je suis surprise. La cause, c'est l'oiseau. D'abord respirer. Ensuite comprendre. Amandine souffle une grande fois. Elle respire encore. Elle regarde. C'est un merle. Il picore. Rien n'est cassé. Je veux comprendre. Plus tard, à la cuisine, maman ouvre un placard. Une boîte glisse. Clac. Amandine sent encore son cœur. Je suis surprise. Même leçon, autre lieu. Elle souffle. Elle respire. Elle regarde. C'est la boîte à farine. Elle veut comprendre. Maman sourit. Être surpris, on peut respirer. Puis on cherche à comprendre.</t>
+          <t>Le romarin sent fort, ce soir. Une abeille tourne tout près. Les pots en terre sont chauds. L'eau tremble dans l'arrosoir. Le gravier craque sous les pas. Un ver se cache sous une feuille. L'arrosoir goutte sur la terre. On arrose tout doux, Nina. Les feuilles ont soif. L'eau est froide, papa. Oui. Les pots sont chauds. En ce moment, Nina arrose les pots. Un oiseau s'envole tout près. Voup. Nina sent son cœur vite. Ses épaules sautent. Je suis surprise. D'abord respirer. Ensuite comprendre. Nina souffle une grande fois. Elle respire encore. Tu as soufflé. Bravo. Qu'est-ce que tu vois ? Je veux comprendre. Nina regarde. C'est un merle. Il picore. Rien n'est cassé. La cause, c'est l'oiseau. Oui. Tu as compris. Plus tard, à la cuisine. Ça sent encore le romarin, dehors. Maman ouvre un placard. Une boîte glisse. Clac. Nina sent encore son cœur. Je suis surprise. D'abord respirer. Nina souffle. Elle respire. Elle regarde. C'est la boîte à farine. Tu veux comprendre. Bravo. Être surpris, on peut respirer. Puis on cherche à comprendre. Nina pose l'arrosoir près de la porte. Un peu de farine reste sur le bois. Tu as soufflé au jardin. Tu as soufflé à la cuisine. Deux fois. Je comprends. Une cuillère en bois attend. Elle sent encore la farine.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,18 +1324,65 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Amandine arrose les pots avec papa. Un oiseau s'envole tout près. Voup. Amandine sent son cœur vite. Ses épaules sautent.
-narrateur|Je suis surprise.
-narrateur|La cause, c'est l'oiseau.
-papa|D'abord respirer. Ensuite comprendre.
-narrateur|Amandine souffle une grande fois. Elle respire encore. Elle regarde. C'est un merle. Il picore. Rien n'est cassé.
-enfant-f|Je veux comprendre. Plus tard, à la cuisine, maman ouvre un placard.
-narrateur|Une boîte glisse. Clac. Amandine sent encore son cœur.
-narrateur|Je suis surprise. Même leçon, autre lieu. Elle souffle. Elle respire.
-narrateur|Elle regarde. C'est la boîte à farine. Elle veut comprendre. Maman sourit. Être surpris, on peut respirer. Puis on cherche à comprendre.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le romarin sent fort, ce soir.
+narrateur|Une abeille tourne tout près.
+narrateur|Les pots en terre sont chauds.
+narrateur|L'eau tremble dans l'arrosoir.
+narrateur|Le gravier craque sous les pas.
+narrateur|Un ver se cache sous une feuille.
+narrateur|L'arrosoir goutte sur la terre.
+papa|On arrose tout doux, Nina.
+maman|Les feuilles ont soif.
+enfant-f|L'eau est froide, papa.
+papa|Oui. Les pots sont chauds.
+narrateur|En ce moment, Nina arrose les pots.
+narrateur|Un oiseau s'envole tout près.
+narrateur|Voup.
+narrateur|Nina sent son cœur vite.
+narrateur|Ses épaules sautent.
+enfant-f|Je suis surprise.
+papa|D'abord respirer.
+papa|Ensuite comprendre.
+narrateur|Nina souffle une grande fois.
+narrateur|Elle respire encore.
+maman|Tu as soufflé. Bravo.
+papa|Qu'est-ce que tu vois ?
+enfant-f|Je veux comprendre.
+narrateur|Nina regarde.
+narrateur|C'est un merle.
+narrateur|Il picore.
+papa|Rien n'est cassé.
+enfant-f|La cause, c'est l'oiseau.
+maman|Oui. Tu as compris.
+narrateur|Plus tard, à la cuisine.
+narrateur|Ça sent encore le romarin, dehors.
+narrateur|Maman ouvre un placard.
+narrateur|Une boîte glisse.
+narrateur|Clac.
+narrateur|Nina sent encore son cœur.
+enfant-f|Je suis surprise.
+maman|D'abord respirer.
+narrateur|Nina souffle.
+narrateur|Elle respire.
+narrateur|Elle regarde.
+enfant-f|C'est la boîte à farine.
+papa|Tu veux comprendre. Bravo.
+maman|Être surpris, on peut respirer.
+papa|Puis on cherche à comprendre.
+narrateur|Nina pose l'arrosoir près de la porte.
+narrateur|Un peu de farine reste sur le bois.
+papa|Tu as soufflé au jardin.
+maman|Tu as soufflé à la cuisine.
+enfant-f|Deux fois. Je comprends.
+narrateur|Une cuillère en bois attend.
+narrateur|Elle sent encore la farine.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>jardin,cuisine</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1348,7 +1407,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Amandine est surprise. Que fait-elle d'abord ?</t>
+          <t>Nina est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1508,7 +1567,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Amandine est surprise. Que fait-elle d'abord ?</t>
+          <t>narrateur|Nina est surprise.
+narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1536,7 +1596,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Amandine a nommé : surprise. Au jardin, puis à la cuisine. Elle a respiré. Elle a voulu comprendre.</t>
+          <t>Nina a nommé : surprise. Au jardin, puis à la cuisine. Elle a respiré. Elle a voulu comprendre. Tu as soufflé deux fois. Bravo. Tu as regardé. Tu as compris. C'était le merle. Puis la farine. Rien n'était cassé. On nomme. On respire. On comprend. Nina essuie un peu de farine. La poudre est douce sous le doigt. On referme la boîte ? Oui. Tout doux. Le merle picore encore, dehors. Nina écoute un instant.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1680,10 +1740,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Amandine a nommé : surprise. Au jardin, puis à la cuisine. Elle a respiré. Elle a voulu comprendre.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Nina a nommé : surprise.
+narrateur|Au jardin, puis à la cuisine.
+narrateur|Elle a respiré.
+narrateur|Elle a voulu comprendre.
+papa|Tu as soufflé deux fois. Bravo.
+maman|Tu as regardé. Tu as compris.
+enfant-f|C'était le merle. Puis la farine.
+papa|Rien n'était cassé.
+maman|On nomme. On respire. On comprend.
+narrateur|Nina essuie un peu de farine.
+narrateur|La poudre est douce sous le doigt.
+papa|On referme la boîte ?
+enfant-f|Oui. Tout doux.
+maman|Le merle picore encore, dehors.
+narrateur|Nina écoute un instant.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>cuisine</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1708,7 +1786,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Amandine range l'arrosoir. Papa referme le placard.</t>
+          <t>Nina range l'arrosoir. Papa referme le placard. On laisse le romarin dehors ? Oui. L'abeille est partie. Tu as nommé. Tu as soufflé. Je suis calme, maintenant. La farine reste dans la boîte. On laisse l'arrosoir près de la porte. Oui. Il goutte encore. Le gravier est encore chaud. La cuisine sent le bois. Le romarin sent encore, dehors.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1844,7 +1922,18 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Amandine range l'arrosoir. Papa referme le placard.</t>
+          <t>narrateur|Nina range l'arrosoir.
+narrateur|Papa referme le placard.
+maman|On laisse le romarin dehors ?
+enfant-f|Oui. L'abeille est partie.
+papa|Tu as nommé. Tu as soufflé.
+enfant-f|Je suis calme, maintenant.
+maman|La farine reste dans la boîte.
+papa|On laisse l'arrosoir près de la porte.
+enfant-f|Oui. Il goutte encore.
+narrateur|Le gravier est encore chaud.
+narrateur|La cuisine sent le bois.
+narrateur|Le romarin sent encore, dehors.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1872,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le merle a picoré. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2012,7 +2101,10 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-f|J'étais surprise. J'ai soufflé.
+papa|Tu as compris. Bravo.
+maman|Le merle a picoré.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2034,7 +2126,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2072,6 +2164,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-07.xlsx
@@ -1189,7 +1189,7 @@
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amandine arrose les pots avec papa. Un oiseau s'envole tout près. Voup. Amandine sent son cœur vite. Ses épaules sautent. Elle dit : je suis &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;e. La cause, c'est l'oiseau. Papa dit : d'abord respirer. Ensuite comprendre. Amandine souffle une grande fois. Elle respire encore. Elle regarde. C'est un merle. Il picore. Rien n'est cassé. Amandine dit : je veux comprendre. Plus tard, à la cuisine, maman ouvre un placard. Une boîte glisse. Clac. Amandine sent encore son cœur. Elle dit : je suis surprise. Même leçon, autre lieu. Elle souffle. Elle respire. Elle regarde. C'est la boîte à farine. Elle veut comprendre. Maman sourit. Être surpris, on peut respirer. Puis on cherche à comprendre.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le romarin sent fort, ce soir. Une abeille tourne tout près. Les pots en terre sont chauds. L'eau tremble dans l'arrosoir. Le gravier craque sous les pas. Un ver se cache sous une feuille. L'arrosoir goutte sur la terre. On arrose tout doux, Nina. Les feuilles ont soif. L'eau est froide, papa. Oui. Les pots sont chauds. En ce moment, Nina arrose les pots. Un oiseau s'envole tout près. Voup. Nina sent son cœur vite. Ses épaules sautent. Je suis surprise. D'abord respirer. Ensuite comprendre. Nina souffle une grande fois. Elle respire encore. Tu as soufflé. Bravo. Qu'est-ce que tu vois ? Je veux comprendre. Nina regarde. C'est un merle. Il picore. Rien n'est cassé. La cause, c'est l'oiseau. Oui. Tu as compris. Plus tard, à la cuisine. Ça sent encore le romarin, dehors. Maman ouvre un placard. Une boîte glisse. Clac. Nina sent encore son cœur. Je suis surprise. D'abord respirer. Nina souffle. Elle respire. Elle regarde. C'est la boîte à farine. Tu veux comprendre. Bravo. Être surpris, on peut respirer. Puis on cherche à comprendre. Nina pose l'arrosoir près de la porte. Un peu de farine reste sur le bois. Tu as soufflé au jardin. Tu as soufflé à la cuisine. Deux fois. Je comprends. Une cuillère en bois attend. Elle sent encore la farine.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1412,7 +1412,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amandine est &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;e. Que fait-elle d'abord ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina est surprise. Que fait-elle d'abord ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1571,7 +1571,6 @@
 narrateur|Que fait-elle d'abord ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1601,7 +1600,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amandine a nommé : &lt;emphasis level="moderate"&gt;surpris&lt;/emphasis&gt;e. Au jardin, puis à la cuisine. Elle a respiré. Elle a voulu comprendre.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina a nommé : surprise. Au jardin, puis à la cuisine. Elle a respiré. Elle a voulu comprendre. Tu as soufflé deux fois. Bravo. Tu as regardé. Tu as compris. C'était le merle. Puis la farine. Rien n'était cassé. On nomme. On respire. On comprend. Nina essuie un peu de farine. La poudre est douce sous le doigt. On referme la boîte ? Oui. Tout doux. Le merle picore encore, dehors. Nina écoute un instant.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1791,7 +1790,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Amandine range l'arrosoir. Papa referme le placard.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Nina range l'arrosoir. Papa referme le placard. On laisse le romarin dehors ? Oui. L'abeille est partie. Tu as nommé. Tu as soufflé. Je suis calme, maintenant. La farine reste dans la boîte. On laisse l'arrosoir près de la porte. Oui. Il goutte encore. Le gravier est encore chaud. La cuisine sent le bois. Le romarin sent encore, dehors.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1936,7 +1935,6 @@
 narrateur|Le romarin sent encore, dehors.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1961,12 +1959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le merle a picoré. L'histoire est finie.</t>
+          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le merle a picoré.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'étais surprise. J'ai soufflé. Tu as compris. Bravo. Le merle a picoré.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2103,11 +2101,9 @@
         <is>
           <t>enfant-f|J'étais surprise. J'ai soufflé.
 papa|Tu as compris. Bravo.
-maman|Le merle a picoré.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+maman|Le merle a picoré.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2126,7 +2122,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2171,6 +2167,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-EMO.LEX.004-07.xlsx
+++ b/stories/arbres/ATOM-EMO.LEX.004-07.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Amandine, papa, maman</t>
+          <t>Nina, papa, maman</t>
         </is>
       </c>
     </row>
